--- a/venv/ImportPoi/test.xlsx
+++ b/venv/ImportPoi/test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin Data\PycharmProjects\pythonProject1\github\Code_python\venv\ImportPoi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED60952-77B9-4D29-B556-95A3D71D0166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D76C6D8-C8C8-4095-9861-11A5235FC0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Name</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>foodyhcm</t>
+  </si>
+  <si>
+    <t>0938260254</t>
   </si>
 </sst>
 </file>
@@ -115,10 +118,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,6 +405,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -437,6 +445,9 @@
       </c>
       <c r="C2" t="s">
         <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="E2">
         <v>10.7519372</v>
